--- a/output/pdf_financials_xlsx/SJ.xlsx
+++ b/output/pdf_financials_xlsx/SJ.xlsx
@@ -5434,10 +5434,10 @@
         <v>64.90000000000001</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>150674</v>
+        <v>150626.4</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>103135</v>
+        <v>103285.7</v>
       </c>
       <c r="N91" s="1" t="inlineStr">
         <is>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="O91" s="3" t="n">
+        <v>421</v>
+      </c>
+      <c r="P91" s="3" t="n">
         <v>166</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>255</v>
       </c>
     </row>
     <row r="92">
@@ -5488,10 +5488,10 @@
         <v>0.298</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>348</v>
+        <v>348.1</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>386</v>
+        <v>386.3</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>TotalNonCurrentLiabilities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/output/pdf_financials_xlsx/SJ.xlsx
+++ b/output/pdf_financials_xlsx/SJ.xlsx
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.191</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.681</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.267</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>6.4</v>
@@ -2402,19 +2402,19 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.191</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.681</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.267</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>6.4</v>
@@ -3050,19 +3050,19 @@
         <v>10.418</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.9</v>
+        <v>17.9</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>15.293</v>
+        <v>12.102</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>22.736</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>49.503</v>
+        <v>46.822</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>35.112</v>
+        <v>32.845</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>20.06</v>
@@ -4238,10 +4238,10 @@
         <v>4</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>9710.799999999999</v>
+        <v>29234.8</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>6549.7</v>
+        <v>19717.7</v>
       </c>
       <c r="N69" s="1" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="O69" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4346,10 +4346,10 @@
         <v>4</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>9710.799999999999</v>
+        <v>29234.8</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>6549.7</v>
+        <v>19717.7</v>
       </c>
       <c r="N71" s="1" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="O75" s="3" t="n">
-        <v>317</v>
+        <v>280</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76">
@@ -4643,7 +4643,7 @@
         <v>100.845</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>87.08</v>
+        <v>82.334</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>82.334</v>
@@ -4670,10 +4670,10 @@
         <v>449.945</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>523291</v>
+        <v>503767</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>611539</v>
+        <v>598371</v>
       </c>
       <c r="N77" s="1" t="inlineStr">
         <is>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="O77" s="3" t="n">
-        <v>2678</v>
+        <v>2641</v>
       </c>
       <c r="P77" s="3" t="n">
-        <v>2760</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="78">
@@ -4751,7 +4751,7 @@
         <v>100.845</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>87.08</v>
+        <v>82.334</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>82.334</v>
@@ -4778,10 +4778,10 @@
         <v>449.945</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>523291</v>
+        <v>503767</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>611539</v>
+        <v>598371</v>
       </c>
       <c r="N79" s="1" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="O79" s="3" t="n">
-        <v>2918</v>
+        <v>2881</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>3019</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="80">
@@ -4805,7 +4805,7 @@
         <v>0.6564315507224787</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.5102068030537066</v>
+        <v>0.4838369134005268</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>0.4850631952451775</v>
@@ -10670,7 +10670,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TotalNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -42859,7 +42859,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -43045,7 +43045,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -45757,7 +45757,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -51678,7 +51678,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -53019,7 +53019,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -55254,7 +55254,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -62073,7 +62073,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">

--- a/output/pdf_financials_xlsx/SJ.xlsx
+++ b/output/pdf_financials_xlsx/SJ.xlsx
@@ -2003,34 +2003,34 @@
         <v>1.883</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>5.502</v>
+        <v>10.353</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4.192</v>
+        <v>8.715</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>5.393</v>
+        <v>10.705</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.561999999999999</v>
+        <v>16.322</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.885</v>
+        <v>20.576</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>10.932</v>
+        <v>23.334</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>15.803</v>
+        <v>31.587</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>15.285</v>
+        <v>33.204</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>17.016</v>
+        <v>38.102</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>14.331</v>
+        <v>38.162</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>109</v>
@@ -2057,34 +2057,34 @@
         <v>43.675</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>55.627</v>
+        <v>60.478</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>84.121</v>
+        <v>88.64400000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>106.67</v>
+        <v>111.982</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>136.369</v>
+        <v>144.129</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>153.583</v>
+        <v>163.274</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>213.894</v>
+        <v>226.296</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>231.187</v>
+        <v>246.971</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>203.664</v>
+        <v>221.583</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>204.215</v>
+        <v>225.301</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>233.013</v>
+        <v>256.844</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>540</v>
@@ -2111,34 +2111,34 @@
         <v>10.62344479335667</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>9.914873290247145</v>
+        <v>10.77950827561376</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>13.14086742440811</v>
+        <v>13.84742278348132</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>14.86702327824344</v>
+        <v>15.60737790141799</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>13.4846582088224</v>
+        <v>14.25199497671291</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>12.29162548329603</v>
+        <v>13.06722006445814</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13.7170099542497</v>
+        <v>14.51234950305707</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>12.57576754845234</v>
+        <v>13.43436217092147</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>10.79791447303544</v>
+        <v>11.7479489879341</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>9.615126562402153</v>
+        <v>10.60792610550532</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.74276298591578</v>
+        <v>11.84146041789322</v>
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
@@ -5847,44 +5847,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.313</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.883</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>10.353</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>8.715</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>10.705</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>16.322</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>20.576</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>23.334</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>31.587</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>33.204</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>38.102</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>38.162</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>109</v>
@@ -6529,10 +6525,10 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -71071,7 +71067,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr"/>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E706" t="inlineStr">
         <is>
           <t>-</t>
@@ -71156,7 +71156,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E707" t="inlineStr">
@@ -73254,7 +73254,11 @@
           <t>Addition of intangible assets</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E731" t="inlineStr">
         <is>
           <t>-</t>
@@ -77496,7 +77500,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E781" t="inlineStr">
         <is>
           <t>-</t>
@@ -77579,7 +77587,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E782" s="5" t="n">
@@ -80284,7 +80292,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E813" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SJ.xlsx
+++ b/output/pdf_financials_xlsx/SJ.xlsx
@@ -2479,10 +2479,8 @@
       <c r="M37" s="3" t="n">
         <v>179161</v>
       </c>
-      <c r="N37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N37" s="3" t="n">
+        <v>270</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>277</v>
@@ -2615,42 +2613,40 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>4.252</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>8.391</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>5.582</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>9.911</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>4.708</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>18.222</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>4.485</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>9.759</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>38</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -2669,31 +2665,31 @@
         <v>30.16</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>76.511</v>
+        <v>80.76300000000001</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>89.563</v>
+        <v>97.95399999999999</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>107.987</v>
+        <v>113.569</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>127.545</v>
+        <v>137.456</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>159.862</v>
+        <v>164.57</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>160.755</v>
+        <v>178.977</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>163.458</v>
+        <v>167.943</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>192380</v>
+        <v>192389.759</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>179161</v>
+        <v>179166</v>
       </c>
       <c r="N41" s="1" t="inlineStr">
         <is>
@@ -2701,10 +2697,10 @@
         </is>
       </c>
       <c r="O41" s="3" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -3047,25 +3043,25 @@
         <v>10.145</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>10.418</v>
+        <v>6.166</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>17.9</v>
+        <v>9.509</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12.102</v>
+        <v>6.52</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>22.736</v>
+        <v>12.825</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46.822</v>
+        <v>42.114</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>32.845</v>
+        <v>14.623</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>20.06</v>
+        <v>15.575</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>35567</v>
@@ -3501,37 +3497,37 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>123.23</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>144.124</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>164.035</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>238.181</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>290.861</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>349.988</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>462.696</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>559.04</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>579.633</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="N56" s="1" t="inlineStr">
         <is>
@@ -3555,37 +3551,37 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>35.546</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>39.361</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>44.594</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>49.153</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>56.627</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
+        <v>68.381</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0</v>
+        <v>87.16200000000001</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>100.449</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0</v>
+        <v>113.577</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="N57" s="1" t="inlineStr">
         <is>
@@ -3947,25 +3943,25 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>22.367</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>24.813</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>20.497</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>28.041</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>25.183</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>31.77</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>41.373</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>53021</v>
@@ -4109,31 +4105,31 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>14.888</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>24.169</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>27.726</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>35.175</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>39.3</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>39.507</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>51.761</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>60.815</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N67" s="1" t="inlineStr">
         <is>
@@ -7070,15 +7066,11 @@
       <c r="K121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L121" s="3" t="n">
+        <v>-4.038</v>
+      </c>
+      <c r="M121" s="3" t="n">
+        <v>-70.649</v>
       </c>
       <c r="N121" s="3" t="n">
         <v>0</v>
@@ -7157,34 +7149,34 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>46.794</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>66.027</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>98.286</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>174.55</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>4.814</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>26.776</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>130.026</v>
       </c>
       <c r="J123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>195.87</v>
       </c>
       <c r="L123" s="1" t="inlineStr">
         <is>
@@ -7269,34 +7261,34 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-10.838</v>
+        <v>35.956</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>-9.041</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-103.932</v>
+        <v>-37.905</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-80.108</v>
+        <v>18.178</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-70.163</v>
+        <v>104.387</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-9.327999999999999</v>
+        <v>-4.514</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>-3.543</v>
+        <v>23.233</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-12.628</v>
+        <v>117.398</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>-59.176</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-11.507</v>
+        <v>184.363</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>-6.705</v>
@@ -72910,7 +72902,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D727" t="inlineStr"/>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E727" t="inlineStr">
         <is>
           <t>-</t>
@@ -75468,7 +75464,11 @@
           <t>Increase in long-term debt 12</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
           <t>-</t>
@@ -78000,7 +78000,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D787" t="inlineStr"/>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E787" s="5" t="n">
         <v>46.794</v>
       </c>
@@ -80854,7 +80858,11 @@
           <t>Operating activities Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E819" t="inlineStr">
         <is>
           <t>-</t>
@@ -83564,7 +83572,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E849" s="5" t="n">
         <v>1.712</v>
       </c>
